--- a/Scripts_vjcortesa/data_output/GS4_25-24_presurveys/vjcortesa_Risk_Perceptiondataset_overview.xlsx
+++ b/Scripts_vjcortesa/data_output/GS4_25-24_presurveys/vjcortesa_Risk_Perceptiondataset_overview.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10102"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tud365-my.sharepoint.com/personal/jcortesarevalo_tudelft_nl/Documents/Documents/TUDelft/18_Game Data Analysis/R data analysis BEPs/Scripts_vjcortesa/data_output/GS4_25-24_presurveys/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tud365-my.sharepoint.com/personal/idattatreya_tudelft_nl/Documents/BEP_copy/BranchInes/Scripts_vjcortesa/data_output/GS4_25-24_presurveys/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="378" documentId="8_{2A57D442-2CDF-480D-BEE8-91F9534C817C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0BAFBCE-C4C7-4CBA-9517-BDFB5D793E8C}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29400" yWindow="500" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="251007" sheetId="4" r:id="rId1"/>
@@ -888,7 +888,7 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1338,24 +1338,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{178A2201-E2FD-43E2-943B-109A10EE95DF}">
   <dimension ref="A1:AA33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="20.7265625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="41.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="44.26953125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="37.08984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="37.08984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="37.08984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="37.08984375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="37.08984375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="37.08984375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="37.08984375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="37.08984375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="39.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="41.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="44.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="37.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="37.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="37.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="37.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="37.1640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="37.1640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="37.1640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="37.1640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="39.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1438,7 +1438,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1518,7 +1518,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1601,7 +1601,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1684,7 +1684,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1767,7 +1767,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1850,7 +1850,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1933,7 +1933,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2016,7 +2016,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2099,7 +2099,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2182,7 +2182,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2265,7 +2265,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2348,7 +2348,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2514,7 +2514,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2597,7 +2597,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2680,7 +2680,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2763,7 +2763,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2846,7 +2846,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2929,7 +2929,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3012,7 +3012,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3095,7 +3095,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3178,7 +3178,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3261,7 +3261,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3344,12 +3344,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="F25" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="F26" t="str">
         <f>+Settings!$F$7</f>
         <v>1 = No, I do not have a flood experience</v>
@@ -3439,7 +3439,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
       <c r="F27" t="str">
         <f>+Settings!$G$7</f>
         <v>2 = Yes, but without disruptions or damages</v>
@@ -3529,7 +3529,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
       <c r="F28" t="str">
         <f>+Settings!$H$7</f>
         <v>3 = Yes, with minor disruptions or damages</v>
@@ -3619,7 +3619,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="F29" t="str">
         <f>+Settings!$I$7</f>
         <v>4 = Yes, with some disruptions or damages</v>
@@ -3709,7 +3709,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="F30" t="str">
         <f>+Settings!$J$7</f>
         <v>5 = Yes, with serious disruptions or damages</v>
@@ -3799,7 +3799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
       <c r="H31" t="str">
         <f>+Settings!$K$8</f>
         <v>6 = Once a day</v>
@@ -3857,7 +3857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="F32" s="7" t="s">
         <v>167</v>
       </c>
@@ -3936,7 +3936,7 @@
         <v>2.347826086956522</v>
       </c>
     </row>
-    <row r="33" spans="6:27" x14ac:dyDescent="0.35">
+    <row r="33" spans="6:27" x14ac:dyDescent="0.2">
       <c r="F33" s="7" t="s">
         <v>168</v>
       </c>
@@ -4023,12 +4023,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F080FEB0-0A46-43B2-ACBB-0A1361BB2262}">
   <dimension ref="A1:AA62"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="20.7265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4111,7 +4111,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4277,7 +4277,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4360,7 +4360,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4443,7 +4443,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4526,7 +4526,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4609,7 +4609,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4692,7 +4692,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4775,7 +4775,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4858,7 +4858,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4941,7 +4941,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -5024,7 +5024,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -5107,7 +5107,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -5190,7 +5190,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -5273,7 +5273,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -5356,7 +5356,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -5439,7 +5439,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -5522,7 +5522,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -5605,7 +5605,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -5688,7 +5688,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -5771,7 +5771,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -5854,7 +5854,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -5937,7 +5937,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -6020,7 +6020,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -6103,7 +6103,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -6186,7 +6186,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -6269,7 +6269,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -6283,7 +6283,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -6366,7 +6366,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -6449,7 +6449,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -6532,7 +6532,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -6615,7 +6615,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -6698,7 +6698,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -6775,7 +6775,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -6858,7 +6858,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -6941,7 +6941,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -7024,7 +7024,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -7107,7 +7107,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -7190,7 +7190,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -7273,7 +7273,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -7356,7 +7356,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -7439,7 +7439,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -7522,7 +7522,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -7605,7 +7605,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -7688,7 +7688,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -7771,7 +7771,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -7854,7 +7854,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
@@ -7937,7 +7937,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -8020,7 +8020,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -8103,7 +8103,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -8186,7 +8186,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -8269,7 +8269,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -8352,12 +8352,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.2">
       <c r="F54" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.2">
       <c r="F55" t="str">
         <f>+Settings!$F$7</f>
         <v>1 = No, I do not have a flood experience</v>
@@ -8447,7 +8447,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.2">
       <c r="F56" t="str">
         <f>+Settings!$G$7</f>
         <v>2 = Yes, but without disruptions or damages</v>
@@ -8537,7 +8537,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:27" x14ac:dyDescent="0.2">
       <c r="F57" t="str">
         <f>+Settings!$H$7</f>
         <v>3 = Yes, with minor disruptions or damages</v>
@@ -8627,7 +8627,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="58" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.2">
       <c r="F58" t="str">
         <f>+Settings!$I$7</f>
         <v>4 = Yes, with some disruptions or damages</v>
@@ -8717,7 +8717,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.2">
       <c r="F59" t="str">
         <f>+Settings!$J$7</f>
         <v>5 = Yes, with serious disruptions or damages</v>
@@ -8807,7 +8807,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.2">
       <c r="H60" t="str">
         <f>+Settings!$K$8</f>
         <v>6 = Once a day</v>
@@ -8865,7 +8865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.2">
       <c r="F61" s="7" t="s">
         <v>167</v>
       </c>
@@ -8944,7 +8944,7 @@
         <v>3.0434782608695654</v>
       </c>
     </row>
-    <row r="62" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:27" x14ac:dyDescent="0.2">
       <c r="F62" s="7" t="s">
         <v>168</v>
       </c>
@@ -9031,12 +9031,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D0BAA33-F1A8-40BD-9C0B-CBC580EA97A9}">
   <dimension ref="A1:AA88"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="20.7265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9107,7 +9107,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -9178,7 +9178,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -9249,7 +9249,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -9320,7 +9320,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -9391,7 +9391,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -9462,7 +9462,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -9533,7 +9533,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -9604,7 +9604,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -9675,7 +9675,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -9746,7 +9746,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -9817,7 +9817,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -9888,7 +9888,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -9959,7 +9959,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -10030,7 +10030,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -10101,7 +10101,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -10172,7 +10172,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -10243,7 +10243,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -10314,7 +10314,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -10385,7 +10385,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -10456,7 +10456,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -10527,7 +10527,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -10598,7 +10598,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -10669,7 +10669,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -10740,7 +10740,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -10811,7 +10811,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -10882,7 +10882,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -10953,7 +10953,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -11024,7 +11024,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -11095,7 +11095,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -11166,7 +11166,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -11237,7 +11237,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -11308,7 +11308,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -11379,7 +11379,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -11450,7 +11450,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -11521,7 +11521,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -11592,7 +11592,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -11663,7 +11663,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -11734,7 +11734,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -11805,7 +11805,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -11876,7 +11876,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -11947,7 +11947,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -12018,7 +12018,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -12089,7 +12089,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -12160,7 +12160,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -12231,7 +12231,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -12302,7 +12302,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -12373,7 +12373,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
@@ -12444,7 +12444,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -12515,7 +12515,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -12586,7 +12586,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -12657,7 +12657,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -12728,7 +12728,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -12799,7 +12799,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
@@ -12870,7 +12870,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -12941,7 +12941,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>55</v>
       </c>
@@ -13012,7 +13012,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
@@ -13083,7 +13083,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
@@ -13154,7 +13154,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>58</v>
       </c>
@@ -13225,7 +13225,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
@@ -13296,7 +13296,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
@@ -13367,7 +13367,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>61</v>
       </c>
@@ -13438,7 +13438,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>62</v>
       </c>
@@ -13509,7 +13509,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>63</v>
       </c>
@@ -13580,7 +13580,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>64</v>
       </c>
@@ -13651,7 +13651,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>65</v>
       </c>
@@ -13722,7 +13722,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>66</v>
       </c>
@@ -13793,7 +13793,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
@@ -13864,7 +13864,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
@@ -13935,7 +13935,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
@@ -14006,7 +14006,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -14077,7 +14077,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
@@ -14148,7 +14148,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
@@ -14219,7 +14219,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
@@ -14290,7 +14290,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>74</v>
       </c>
@@ -14361,7 +14361,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>75</v>
       </c>
@@ -14432,7 +14432,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>76</v>
       </c>
@@ -14503,7 +14503,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>77</v>
       </c>
@@ -14574,7 +14574,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>78</v>
       </c>
@@ -14645,12 +14645,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:23" x14ac:dyDescent="0.2">
       <c r="F80" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="81" spans="6:27" x14ac:dyDescent="0.35">
+    <row r="81" spans="6:27" x14ac:dyDescent="0.2">
       <c r="F81" t="str">
         <f>+Settings!$F$7</f>
         <v>1 = No, I do not have a flood experience</v>
@@ -14724,7 +14724,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="82" spans="6:27" x14ac:dyDescent="0.35">
+    <row r="82" spans="6:27" x14ac:dyDescent="0.2">
       <c r="F82" t="str">
         <f>+Settings!$G$7</f>
         <v>2 = Yes, but without disruptions or damages</v>
@@ -14798,7 +14798,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="83" spans="6:27" x14ac:dyDescent="0.35">
+    <row r="83" spans="6:27" x14ac:dyDescent="0.2">
       <c r="F83" t="str">
         <f>+Settings!$H$7</f>
         <v>3 = Yes, with minor disruptions or damages</v>
@@ -14872,7 +14872,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="84" spans="6:27" x14ac:dyDescent="0.35">
+    <row r="84" spans="6:27" x14ac:dyDescent="0.2">
       <c r="F84" t="str">
         <f>+Settings!$I$7</f>
         <v>4 = Yes, with some disruptions or damages</v>
@@ -14946,7 +14946,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="85" spans="6:27" x14ac:dyDescent="0.35">
+    <row r="85" spans="6:27" x14ac:dyDescent="0.2">
       <c r="F85" t="str">
         <f>+Settings!$J$7</f>
         <v>5 = Yes, with serious disruptions or damages</v>
@@ -15020,7 +15020,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="6:27" x14ac:dyDescent="0.35">
+    <row r="86" spans="6:27" x14ac:dyDescent="0.2">
       <c r="H86" t="str">
         <f>+Settings!$K$8</f>
         <v>6 = Once a day</v>
@@ -15062,7 +15062,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="6:27" x14ac:dyDescent="0.35">
+    <row r="87" spans="6:27" x14ac:dyDescent="0.2">
       <c r="F87" s="7" t="s">
         <v>167</v>
       </c>
@@ -15131,7 +15131,7 @@
       <c r="Z87" s="7"/>
       <c r="AA87" s="8"/>
     </row>
-    <row r="88" spans="6:27" x14ac:dyDescent="0.35">
+    <row r="88" spans="6:27" x14ac:dyDescent="0.2">
       <c r="F88" s="7" t="s">
         <v>168</v>
       </c>
@@ -15206,21 +15206,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4202AC7-E120-46FE-93A3-75166DB6F668}">
   <dimension ref="A1:L18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.6328125" customWidth="1"/>
-    <col min="2" max="2" width="16.81640625" customWidth="1"/>
-    <col min="3" max="3" width="53.54296875" customWidth="1"/>
-    <col min="5" max="5" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.453125" customWidth="1"/>
-    <col min="7" max="7" width="32.453125" customWidth="1"/>
-    <col min="8" max="8" width="24.08984375" customWidth="1"/>
-    <col min="9" max="9" width="21.36328125" customWidth="1"/>
-    <col min="10" max="10" width="26.453125" customWidth="1"/>
-    <col min="11" max="11" width="21.26953125" customWidth="1"/>
+    <col min="1" max="1" width="21.6640625" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="53.5" customWidth="1"/>
+    <col min="5" max="5" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.5" customWidth="1"/>
+    <col min="7" max="7" width="32.5" customWidth="1"/>
+    <col min="8" max="8" width="24.1640625" customWidth="1"/>
+    <col min="9" max="9" width="21.33203125" customWidth="1"/>
+    <col min="10" max="10" width="26.5" customWidth="1"/>
+    <col min="11" max="11" width="21.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>154</v>
       </c>
@@ -15258,7 +15258,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" t="str">
         <f>+[1]Overview!A2</f>
         <v>Presurvey_id-0-1</v>
@@ -15276,7 +15276,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" t="str">
         <f>+[1]Overview!A3</f>
         <v>Presurvey_id-0-2</v>
@@ -15294,7 +15294,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" t="str">
         <f>+[1]Overview!A4</f>
         <v>Presurvey_id-0-3</v>
@@ -15318,7 +15318,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" t="str">
         <f>+[1]Overview!A5</f>
         <v>Presurvey_id-0-4</v>
@@ -15336,7 +15336,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A6">
         <f>+[1]Overview!A8</f>
         <v>0</v>
@@ -15354,7 +15354,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" t="str">
         <f>+[1]Overview!A10</f>
         <v>RiskPerception_1</v>
@@ -15387,7 +15387,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="str">
         <f>+[1]Overview!A12</f>
         <v>RiskPerception_2_1</v>
@@ -15423,7 +15423,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" t="str">
         <f>+[1]Overview!A13</f>
         <v>RiskPerception_2_2</v>
@@ -15466,7 +15466,7 @@
         <v>6 = Once a day</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" t="str">
         <f>+[1]Overview!A14</f>
         <v>RiskPerception_2_3</v>
@@ -15509,7 +15509,7 @@
         <v>6 = Once a day</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" t="str">
         <f>+[1]Overview!A15</f>
         <v>RiskPerception_2_4</v>
@@ -15552,7 +15552,7 @@
         <v>6 = Once a day</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" t="str">
         <f>+[1]Overview!A16</f>
         <v>RiskPerception_2_5</v>
@@ -15595,7 +15595,7 @@
         <v>6 = Once a day</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" t="str">
         <f>+[1]Overview!A17</f>
         <v>RiskPerception_2_6</v>
@@ -15638,7 +15638,7 @@
         <v>6 = Once a day</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" t="str">
         <f>+[1]Overview!A18</f>
         <v>RiskPerception_2_7</v>
@@ -15681,7 +15681,7 @@
         <v>6 = Once a day</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A15">
         <f>+[1]Overview!A19</f>
         <v>0</v>
@@ -15705,7 +15705,7 @@
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
     </row>
-    <row r="16" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A16" t="str">
         <f>+[1]Overview!A20</f>
         <v>RiskPerception_3</v>
@@ -15738,7 +15738,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A17" t="str">
         <f>+[1]Overview!A21</f>
         <v>RiskPerception_4</v>
@@ -15771,7 +15771,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A18" t="str">
         <f>+[1]Overview!A22</f>
         <v>RiskPerception_5</v>
@@ -15812,31 +15812,31 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DB62900-88B7-4FC3-B57C-5FD835749EC5}">
   <dimension ref="A1:AB162"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="20.7265625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="10.453125" customWidth="1"/>
-    <col min="6" max="6" width="15.6328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="45.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="10.5" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="45.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.90625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="35.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="35.453125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="35.453125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="24.54296875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="35.453125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="22.453125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="35.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="35.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="35.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="35.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="35.5" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="18" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="35.453125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="20.54296875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="34.90625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="35.5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="34.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>246</v>
       </c>
@@ -15910,7 +15910,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>251007</v>
       </c>
@@ -16007,7 +16007,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>251007</v>
       </c>
@@ -16104,7 +16104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>251007</v>
       </c>
@@ -16201,7 +16201,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>251007</v>
       </c>
@@ -16298,7 +16298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>251007</v>
       </c>
@@ -16395,7 +16395,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>251007</v>
       </c>
@@ -16492,7 +16492,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>251007</v>
       </c>
@@ -16589,7 +16589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>251007</v>
       </c>
@@ -16686,7 +16686,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>251007</v>
       </c>
@@ -16783,7 +16783,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>251007</v>
       </c>
@@ -16880,7 +16880,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>251007</v>
       </c>
@@ -16977,7 +16977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>251007</v>
       </c>
@@ -17074,7 +17074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>251007</v>
       </c>
@@ -17171,7 +17171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>251007</v>
       </c>
@@ -17268,7 +17268,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>251007</v>
       </c>
@@ -17365,7 +17365,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>251007</v>
       </c>
@@ -17462,7 +17462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>251007</v>
       </c>
@@ -17559,7 +17559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>251007</v>
       </c>
@@ -17656,7 +17656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>251007</v>
       </c>
@@ -17753,7 +17753,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>251007</v>
       </c>
@@ -17850,7 +17850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>251007</v>
       </c>
@@ -17947,7 +17947,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>251007</v>
       </c>
@@ -18044,7 +18044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>251007</v>
       </c>
@@ -18141,7 +18141,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B25">
         <f>+'250923'!A2</f>
         <v>1</v>
@@ -18235,7 +18235,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B26">
         <f>+'250923'!A3</f>
         <v>2</v>
@@ -18329,7 +18329,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B27">
         <f>+'250923'!A4</f>
         <v>3</v>
@@ -18423,7 +18423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B28">
         <f>+'250923'!A5</f>
         <v>4</v>
@@ -18517,7 +18517,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B29">
         <f>+'250923'!A6</f>
         <v>5</v>
@@ -18611,7 +18611,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B30">
         <f>+'250923'!A7</f>
         <v>6</v>
@@ -18705,7 +18705,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B31">
         <f>+'250923'!A8</f>
         <v>7</v>
@@ -18799,7 +18799,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B32">
         <f>+'250923'!A9</f>
         <v>8</v>
@@ -18893,7 +18893,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B33">
         <f>+'250923'!A10</f>
         <v>9</v>
@@ -18987,7 +18987,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B34">
         <f>+'250923'!A11</f>
         <v>10</v>
@@ -19081,7 +19081,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B35">
         <f>+'250923'!A12</f>
         <v>11</v>
@@ -19175,7 +19175,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B36">
         <f>+'250923'!A13</f>
         <v>12</v>
@@ -19269,7 +19269,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37">
         <f>+'250923'!A14</f>
         <v>13</v>
@@ -19363,7 +19363,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B38">
         <f>+'250923'!A15</f>
         <v>14</v>
@@ -19457,7 +19457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B39">
         <f>+'250923'!A16</f>
         <v>15</v>
@@ -19551,7 +19551,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B40">
         <f>+'250923'!A17</f>
         <v>16</v>
@@ -19645,7 +19645,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B41">
         <f>+'250923'!A18</f>
         <v>17</v>
@@ -19739,7 +19739,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B42">
         <f>+'250923'!A19</f>
         <v>18</v>
@@ -19833,7 +19833,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B43">
         <f>+'250923'!A20</f>
         <v>19</v>
@@ -19927,7 +19927,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B44">
         <f>+'250923'!A21</f>
         <v>20</v>
@@ -20021,7 +20021,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B45">
         <f>+'250923'!A22</f>
         <v>21</v>
@@ -20115,7 +20115,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B46">
         <f>+'250923'!A23</f>
         <v>22</v>
@@ -20209,7 +20209,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B47">
         <f>+'250923'!A24</f>
         <v>23</v>
@@ -20303,7 +20303,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B48">
         <f>+'250923'!A25</f>
         <v>24</v>
@@ -20397,7 +20397,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B49">
         <f>+'250923'!A26</f>
         <v>25</v>
@@ -20491,7 +20491,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B50">
         <f>+'250923'!A27</f>
         <v>26</v>
@@ -20585,7 +20585,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B51">
         <f>+'250923'!A28</f>
         <v>27</v>
@@ -20679,7 +20679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B52">
         <f>+'250923'!A29</f>
         <v>28</v>
@@ -20773,7 +20773,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B53">
         <f>+'250923'!A30</f>
         <v>29</v>
@@ -20867,7 +20867,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B54">
         <f>+'250923'!A31</f>
         <v>30</v>
@@ -20961,7 +20961,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B55">
         <f>+'250923'!A32</f>
         <v>31</v>
@@ -21055,7 +21055,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B56">
         <f>+'250923'!A33</f>
         <v>32</v>
@@ -21149,7 +21149,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B57">
         <f>+'250923'!A34</f>
         <v>33</v>
@@ -21243,7 +21243,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B58">
         <f>+'250923'!A35</f>
         <v>34</v>
@@ -21337,7 +21337,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B59">
         <f>+'250923'!A36</f>
         <v>35</v>
@@ -21431,7 +21431,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B60">
         <f>+'250923'!A37</f>
         <v>36</v>
@@ -21525,7 +21525,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B61">
         <f>+'250923'!A38</f>
         <v>37</v>
@@ -21619,7 +21619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B62">
         <f>+'250923'!A39</f>
         <v>38</v>
@@ -21713,7 +21713,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B63">
         <f>+'250923'!A40</f>
         <v>39</v>
@@ -21807,7 +21807,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B64">
         <f>+'250923'!A41</f>
         <v>40</v>
@@ -21901,7 +21901,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B65">
         <f>+'250923'!A42</f>
         <v>41</v>
@@ -21995,7 +21995,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B66">
         <f>+'250923'!A43</f>
         <v>42</v>
@@ -22089,7 +22089,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B67">
         <f>+'250923'!A44</f>
         <v>43</v>
@@ -22183,7 +22183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B68">
         <f>+'250923'!A45</f>
         <v>44</v>
@@ -22277,7 +22277,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B69">
         <f>+'250923'!A46</f>
         <v>45</v>
@@ -22371,7 +22371,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B70">
         <f>+'250923'!A47</f>
         <v>46</v>
@@ -22465,7 +22465,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B71">
         <f>+'250923'!A48</f>
         <v>47</v>
@@ -22559,7 +22559,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B72">
         <f>+'250923'!A49</f>
         <v>48</v>
@@ -22653,7 +22653,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B73">
         <f>+'250923'!A50</f>
         <v>49</v>
@@ -22747,7 +22747,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B74">
         <f>+'250923'!A51</f>
         <v>50</v>
@@ -22841,7 +22841,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B75">
         <f>+'250923'!A52</f>
         <v>51</v>
@@ -22935,7 +22935,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B76">
         <f>+'250923'!A53</f>
         <v>52</v>
@@ -23029,7 +23029,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B77">
         <f>+'240924'!A2</f>
         <v>1</v>
@@ -23123,7 +23123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B78">
         <f>+'240924'!A3</f>
         <v>2</v>
@@ -23217,7 +23217,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79">
         <f>+'240924'!A4</f>
         <v>3</v>
@@ -23311,7 +23311,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B80">
         <f>+'240924'!A5</f>
         <v>4</v>
@@ -23405,7 +23405,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B81">
         <f>+'240924'!A6</f>
         <v>5</v>
@@ -23499,7 +23499,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B82">
         <f>+'240924'!A7</f>
         <v>6</v>
@@ -23593,7 +23593,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B83">
         <f>+'240924'!A8</f>
         <v>7</v>
@@ -23687,7 +23687,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B84">
         <f>+'240924'!A9</f>
         <v>8</v>
@@ -23781,7 +23781,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B85">
         <f>+'240924'!A10</f>
         <v>9</v>
@@ -23875,7 +23875,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B86">
         <f>+'240924'!A11</f>
         <v>10</v>
@@ -23969,7 +23969,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B87">
         <f>+'240924'!A12</f>
         <v>11</v>
@@ -24063,7 +24063,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B88">
         <f>+'240924'!A13</f>
         <v>12</v>
@@ -24157,7 +24157,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B89">
         <f>+'240924'!A14</f>
         <v>13</v>
@@ -24251,7 +24251,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B90">
         <f>+'240924'!A15</f>
         <v>14</v>
@@ -24345,7 +24345,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B91">
         <f>+'240924'!A16</f>
         <v>15</v>
@@ -24439,7 +24439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B92">
         <f>+'240924'!A17</f>
         <v>16</v>
@@ -24533,7 +24533,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="93" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B93">
         <f>+'240924'!A18</f>
         <v>17</v>
@@ -24627,7 +24627,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B94">
         <f>+'240924'!A19</f>
         <v>18</v>
@@ -24721,7 +24721,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B95">
         <f>+'240924'!A20</f>
         <v>19</v>
@@ -24815,7 +24815,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B96">
         <f>+'240924'!A21</f>
         <v>20</v>
@@ -24909,7 +24909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B97">
         <f>+'240924'!A22</f>
         <v>21</v>
@@ -25003,7 +25003,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="98" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B98">
         <f>+'240924'!A23</f>
         <v>22</v>
@@ -25097,7 +25097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B99">
         <f>+'240924'!A24</f>
         <v>23</v>
@@ -25191,7 +25191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B100">
         <f>+'240924'!A25</f>
         <v>24</v>
@@ -25285,7 +25285,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B101">
         <f>+'240924'!A26</f>
         <v>25</v>
@@ -25379,7 +25379,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B102">
         <f>+'240924'!A27</f>
         <v>26</v>
@@ -25473,7 +25473,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B103">
         <f>+'240924'!A28</f>
         <v>27</v>
@@ -25567,7 +25567,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B104">
         <f>+'240924'!A29</f>
         <v>28</v>
@@ -25661,7 +25661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B105">
         <f>+'240924'!A30</f>
         <v>29</v>
@@ -25755,7 +25755,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="106" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B106">
         <f>+'240924'!A31</f>
         <v>30</v>
@@ -25849,7 +25849,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B107">
         <f>+'240924'!A32</f>
         <v>31</v>
@@ -25943,7 +25943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B108">
         <f>+'240924'!A33</f>
         <v>32</v>
@@ -26037,7 +26037,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B109">
         <f>+'240924'!A34</f>
         <v>33</v>
@@ -26131,7 +26131,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B110">
         <f>+'240924'!A35</f>
         <v>34</v>
@@ -26225,7 +26225,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="111" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B111">
         <f>+'240924'!A36</f>
         <v>35</v>
@@ -26319,7 +26319,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="112" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B112">
         <f>+'240924'!A37</f>
         <v>36</v>
@@ -26413,7 +26413,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="113" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="113" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B113">
         <f>+'240924'!A38</f>
         <v>37</v>
@@ -26507,7 +26507,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="114" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B114">
         <f>+'240924'!A39</f>
         <v>38</v>
@@ -26601,7 +26601,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="115" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B115">
         <f>+'240924'!A40</f>
         <v>39</v>
@@ -26695,7 +26695,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="116" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B116">
         <f>+'240924'!A41</f>
         <v>40</v>
@@ -26789,7 +26789,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="117" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B117">
         <f>+'240924'!A42</f>
         <v>41</v>
@@ -26883,7 +26883,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="118" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B118">
         <f>+'240924'!A43</f>
         <v>42</v>
@@ -26977,7 +26977,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="119" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B119">
         <f>+'240924'!A44</f>
         <v>43</v>
@@ -27071,7 +27071,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="120" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="120" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B120">
         <f>+'240924'!A45</f>
         <v>44</v>
@@ -27165,7 +27165,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="121" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="121" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B121">
         <f>+'240924'!A46</f>
         <v>45</v>
@@ -27259,7 +27259,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="122" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="122" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B122">
         <f>+'240924'!A47</f>
         <v>46</v>
@@ -27353,7 +27353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="123" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B123">
         <f>+'240924'!A48</f>
         <v>47</v>
@@ -27447,7 +27447,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="124" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="124" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B124">
         <f>+'240924'!A49</f>
         <v>48</v>
@@ -27541,7 +27541,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="125" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="125" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B125">
         <f>+'240924'!A50</f>
         <v>49</v>
@@ -27635,7 +27635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="126" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B126">
         <f>+'240924'!A51</f>
         <v>50</v>
@@ -27729,7 +27729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="127" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B127">
         <f>+'240924'!A52</f>
         <v>51</v>
@@ -27823,7 +27823,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="128" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="128" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B128">
         <f>+'240924'!A53</f>
         <v>52</v>
@@ -27917,7 +27917,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="129" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="129" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B129">
         <f>+'240924'!A54</f>
         <v>53</v>
@@ -28011,7 +28011,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="130" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B130">
         <f>+'240924'!A55</f>
         <v>54</v>
@@ -28105,7 +28105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="131" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B131">
         <f>+'240924'!A56</f>
         <v>55</v>
@@ -28199,7 +28199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="132" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B132">
         <f>+'240924'!A57</f>
         <v>56</v>
@@ -28293,7 +28293,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="133" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="133" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B133">
         <f>+'240924'!A58</f>
         <v>57</v>
@@ -28387,7 +28387,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="134" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="134" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B134">
         <f>+'240924'!A59</f>
         <v>58</v>
@@ -28481,7 +28481,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="135" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="135" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B135">
         <f>+'240924'!A60</f>
         <v>59</v>
@@ -28575,7 +28575,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="136" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B136">
         <f>+'240924'!A61</f>
         <v>60</v>
@@ -28669,7 +28669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="137" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B137">
         <f>+'240924'!A62</f>
         <v>61</v>
@@ -28763,7 +28763,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="138" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="138" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B138">
         <f>+'240924'!A63</f>
         <v>62</v>
@@ -28857,7 +28857,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="139" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="139" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B139">
         <f>+'240924'!A64</f>
         <v>63</v>
@@ -28951,7 +28951,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="140" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B140">
         <f>+'240924'!A65</f>
         <v>64</v>
@@ -29045,7 +29045,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="141" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B141">
         <f>+'240924'!A66</f>
         <v>65</v>
@@ -29139,7 +29139,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="142" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="142" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B142">
         <f>+'240924'!A67</f>
         <v>66</v>
@@ -29233,7 +29233,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="143" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="143" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B143">
         <f>+'240924'!A68</f>
         <v>67</v>
@@ -29327,7 +29327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="144" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B144">
         <f>+'240924'!A69</f>
         <v>68</v>
@@ -29421,7 +29421,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="145" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="145" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B145">
         <f>+'240924'!A70</f>
         <v>69</v>
@@ -29515,7 +29515,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="146" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="146" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B146">
         <f>+'240924'!A71</f>
         <v>70</v>
@@ -29609,7 +29609,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="147" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="147" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B147">
         <f>+'240924'!A72</f>
         <v>71</v>
@@ -29703,7 +29703,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="148" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B148">
         <f>+'240924'!A73</f>
         <v>72</v>
@@ -29797,7 +29797,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="149" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="149" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B149">
         <f>+'240924'!A74</f>
         <v>73</v>
@@ -29891,7 +29891,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="150" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="150" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B150">
         <f>+'240924'!A75</f>
         <v>74</v>
@@ -29985,7 +29985,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="151" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="151" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B151">
         <f>+'240924'!A76</f>
         <v>75</v>
@@ -30079,7 +30079,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="152" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="152" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B152">
         <f>+'240924'!A77</f>
         <v>76</v>
@@ -30173,7 +30173,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="153" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="153" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B153">
         <f>+'240924'!A78</f>
         <v>77</v>
@@ -30267,7 +30267,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="154" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="154" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B154">
         <f>+'240924'!A79</f>
         <v>78</v>
@@ -30361,7 +30361,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="155" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="155" spans="2:24" x14ac:dyDescent="0.2">
       <c r="G155" t="str">
         <f>+Settings!$F$7</f>
         <v>1 = No, I do not have a flood experience</v>
@@ -30435,7 +30435,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="156" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="156" spans="2:24" x14ac:dyDescent="0.2">
       <c r="G156" t="str">
         <f>+Settings!$G$7</f>
         <v>2 = Yes, but without disruptions or damages</v>
@@ -30509,7 +30509,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="157" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="157" spans="2:24" x14ac:dyDescent="0.2">
       <c r="G157" t="str">
         <f>+Settings!$H$7</f>
         <v>3 = Yes, with minor disruptions or damages</v>
@@ -30583,7 +30583,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="158" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="158" spans="2:24" x14ac:dyDescent="0.2">
       <c r="G158" t="str">
         <f>+Settings!$I$7</f>
         <v>4 = Yes, with some disruptions or damages</v>
@@ -30657,7 +30657,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="159" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="159" spans="2:24" x14ac:dyDescent="0.2">
       <c r="G159" t="str">
         <f>+Settings!$J$7</f>
         <v>5 = Yes, with serious disruptions or damages</v>
@@ -30731,7 +30731,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="160" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="160" spans="2:24" x14ac:dyDescent="0.2">
       <c r="I160" t="str">
         <f>+Settings!$K$8</f>
         <v>6 = Once a day</v>
@@ -30773,7 +30773,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="161" spans="7:28" x14ac:dyDescent="0.35">
+    <row r="161" spans="7:28" x14ac:dyDescent="0.2">
       <c r="G161" s="7" t="s">
         <v>167</v>
       </c>
@@ -30842,7 +30842,7 @@
       <c r="AA161" s="7"/>
       <c r="AB161" s="8"/>
     </row>
-    <row r="162" spans="7:28" x14ac:dyDescent="0.35">
+    <row r="162" spans="7:28" x14ac:dyDescent="0.2">
       <c r="G162" s="7" t="s">
         <v>168</v>
       </c>
@@ -30917,13 +30917,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3673EA6F-824E-4E44-A989-78DAB71843D4}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="38.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>248</v>
       </c>
@@ -30940,7 +30940,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="str">
         <f>+'251007'!F26</f>
         <v>1 = No, I do not have a flood experience</v>
@@ -30962,7 +30962,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="str">
         <f>+'251007'!F27</f>
         <v>2 = Yes, but without disruptions or damages</v>
@@ -30984,7 +30984,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="str">
         <f>+'251007'!F28</f>
         <v>3 = Yes, with minor disruptions or damages</v>
@@ -31006,7 +31006,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="str">
         <f>+'251007'!F29</f>
         <v>4 = Yes, with some disruptions or damages</v>
@@ -31028,7 +31028,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="str">
         <f>+'251007'!F30</f>
         <v>5 = Yes, with serious disruptions or damages</v>
@@ -31050,7 +31050,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>222</v>
       </c>
@@ -31071,7 +31071,7 @@
         <v>1.3913043478260869</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>168</v>
       </c>
@@ -31092,13 +31092,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="str">
         <f>+'251007'!H1</f>
         <v>Q_Info_G$overnment</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="str">
         <f>+'251007'!H26</f>
         <v>1 = Never</v>
@@ -31108,7 +31108,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="str">
         <f>+'251007'!H27</f>
         <v>2 = Once in the last year</v>
@@ -31118,7 +31118,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="str">
         <f>+'251007'!H28</f>
         <v>3 = Once in the last six months</v>
@@ -31128,7 +31128,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="str">
         <f>+'251007'!H29</f>
         <v>4 = Once a month</v>
@@ -31138,7 +31138,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="str">
         <f>+'251007'!H30</f>
         <v>5 = Once a week</v>
@@ -31148,7 +31148,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="str">
         <f>+'251007'!H31</f>
         <v>6 = Once a day</v>
@@ -31158,7 +31158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>222</v>
       </c>
@@ -31167,7 +31167,7 @@
         <v>2.5217391304347827</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>168</v>
       </c>
